--- a/107女生宿舍名单.xlsx
+++ b/107女生宿舍名单.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\infomation-of-107\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\infomation-of-107\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="41">
   <si>
     <t>107班主任纪亚东
 17611228667</t>
@@ -68,13 +68,7 @@
     <t>女</t>
   </si>
   <si>
-    <t>15729279897</t>
-  </si>
-  <si>
     <t>高灿</t>
-  </si>
-  <si>
-    <t>15703933753</t>
   </si>
   <si>
     <r>
@@ -106,16 +100,10 @@
     </r>
   </si>
   <si>
-    <t>13939363372</t>
-  </si>
-  <si>
     <t>走读留铺</t>
   </si>
   <si>
     <t>曹瑞洋</t>
-  </si>
-  <si>
-    <t>13598736538</t>
   </si>
   <si>
     <r>
@@ -138,13 +126,7 @@
     </r>
   </si>
   <si>
-    <t>13673021779</t>
-  </si>
-  <si>
     <t>张静雪</t>
-  </si>
-  <si>
-    <t>18639341832</t>
   </si>
   <si>
     <r>
@@ -167,133 +149,73 @@
     </r>
   </si>
   <si>
-    <t>13461656277</t>
-  </si>
-  <si>
     <t>刘艺诺</t>
   </si>
   <si>
-    <t>13839351366</t>
-  </si>
-  <si>
     <t>3-2-222</t>
   </si>
   <si>
     <t>于夕露</t>
   </si>
   <si>
-    <t>13721799805</t>
-  </si>
-  <si>
     <t>李静可</t>
   </si>
   <si>
-    <t>13653933521</t>
-  </si>
-  <si>
     <t>陈一诺</t>
   </si>
   <si>
-    <t>15539326958</t>
-  </si>
-  <si>
     <t>刘紫涵</t>
   </si>
   <si>
-    <t>13949735762</t>
-  </si>
-  <si>
     <t>李依柔</t>
   </si>
   <si>
-    <t>18568818855</t>
-  </si>
-  <si>
     <t>段宛辰</t>
   </si>
   <si>
     <t>秦乙涵</t>
   </si>
   <si>
-    <t>15839336710</t>
-  </si>
-  <si>
     <t>郭展孜</t>
   </si>
   <si>
-    <t>19639399998</t>
-  </si>
-  <si>
     <t>3-2-211</t>
   </si>
   <si>
     <t>胡心怡</t>
   </si>
   <si>
-    <t>15936754215</t>
-  </si>
-  <si>
     <t>胡钰涵</t>
   </si>
   <si>
-    <t>13525618067</t>
-  </si>
-  <si>
     <t>杨雨露</t>
   </si>
   <si>
-    <t>13939392757</t>
-  </si>
-  <si>
     <t>杨亚静</t>
   </si>
   <si>
-    <t>13461709630</t>
-  </si>
-  <si>
     <t>李佳涵</t>
   </si>
   <si>
-    <t>13783934087</t>
-  </si>
-  <si>
     <t>史宋涵</t>
   </si>
   <si>
-    <t>13938309563</t>
-  </si>
-  <si>
     <t>苏韵之</t>
   </si>
   <si>
-    <t>18239371983</t>
-  </si>
-  <si>
     <t>郝苗苗</t>
   </si>
   <si>
-    <t>13461702187</t>
-  </si>
-  <si>
     <t>3-2-210</t>
   </si>
   <si>
     <t>孙晨歌</t>
   </si>
   <si>
-    <t>15939323292</t>
-  </si>
-  <si>
     <t>张梦朵</t>
   </si>
   <si>
-    <t>13603839494</t>
-  </si>
-  <si>
     <t>宋佳怡</t>
-  </si>
-  <si>
-    <t>18039355500</t>
   </si>
 </sst>
 </file>
@@ -939,7 +861,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1535,8 +1457,8 @@
       <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>11</v>
+      <c r="E3" s="6">
+        <v>15729279897</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1550,13 +1472,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>13</v>
+      <c r="E4" s="6">
+        <v>15703933753</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -1570,19 +1492,19 @@
         <v>8</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>15</v>
+      <c r="E5" s="6">
+        <v>13939363372</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1593,13 +1515,13 @@
         <v>8</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>18</v>
+      <c r="E6" s="6">
+        <v>13598736538</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -1613,19 +1535,19 @@
         <v>8</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>20</v>
+      <c r="E7" s="6">
+        <v>13673021779</v>
       </c>
       <c r="F7">
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1636,13 +1558,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>22</v>
+      <c r="E8" s="6">
+        <v>18639341832</v>
       </c>
       <c r="F8">
         <v>6</v>
@@ -1656,19 +1578,19 @@
         <v>8</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>24</v>
+      <c r="E9" s="6">
+        <v>13461656277</v>
       </c>
       <c r="F9">
         <v>7</v>
       </c>
       <c r="G9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1679,13 +1601,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>26</v>
+      <c r="E10" s="6">
+        <v>13839351366</v>
       </c>
       <c r="F10">
         <v>8</v>
@@ -1696,22 +1618,22 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>29</v>
+      <c r="E11" s="6">
+        <v>13721799805</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1719,16 +1641,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>31</v>
+      <c r="E12" s="6">
+        <v>13653933521</v>
       </c>
       <c r="F12">
         <v>2</v>
@@ -1739,22 +1661,22 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>33</v>
+      <c r="E13" s="6">
+        <v>15539326958</v>
       </c>
       <c r="F13">
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1762,16 +1684,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>35</v>
+      <c r="E14" s="6">
+        <v>13949735762</v>
       </c>
       <c r="F14">
         <v>4</v>
@@ -1782,22 +1704,22 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>37</v>
+      <c r="E15" s="6">
+        <v>18568818855</v>
       </c>
       <c r="F15">
         <v>5</v>
       </c>
       <c r="G15" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1805,15 +1727,15 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="2">
         <v>13903937336</v>
       </c>
       <c r="F16">
@@ -1825,22 +1747,22 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>40</v>
+      <c r="E17" s="6">
+        <v>15839336710</v>
       </c>
       <c r="F17">
         <v>7</v>
       </c>
       <c r="G17" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1848,16 +1770,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>41</v>
-      </c>
       <c r="D18" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>42</v>
+      <c r="E18" s="6">
+        <v>19639399998</v>
       </c>
       <c r="F18">
         <v>8</v>
@@ -1868,22 +1790,22 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>45</v>
+      <c r="E19" s="6">
+        <v>15936754215</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1891,16 +1813,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>47</v>
+      <c r="E20" s="6">
+        <v>13525618067</v>
       </c>
       <c r="F20">
         <v>2</v>
@@ -1911,16 +1833,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D21" t="s">
         <v>10</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>49</v>
+      <c r="E21" s="6">
+        <v>13939392757</v>
       </c>
       <c r="F21">
         <v>3</v>
@@ -1931,16 +1853,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>51</v>
+      <c r="E22" s="6">
+        <v>13461709630</v>
       </c>
       <c r="F22">
         <v>4</v>
@@ -1951,16 +1873,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="D23" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>53</v>
+      <c r="E23" s="6">
+        <v>13783934087</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -1971,16 +1893,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>55</v>
+      <c r="E24" s="6">
+        <v>13938309563</v>
       </c>
       <c r="F24">
         <v>6</v>
@@ -1991,22 +1913,22 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>57</v>
+      <c r="E25" s="6">
+        <v>18239371983</v>
       </c>
       <c r="F25">
         <v>7</v>
       </c>
       <c r="G25" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2014,16 +1936,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="6" t="s">
-        <v>59</v>
+      <c r="E26" s="6">
+        <v>13461702187</v>
       </c>
       <c r="F26">
         <v>8</v>
@@ -2034,22 +1956,22 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
       </c>
-      <c r="E27" s="6" t="s">
-        <v>62</v>
+      <c r="E27" s="6">
+        <v>15939323292</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2057,22 +1979,22 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
       </c>
-      <c r="E28" s="6" t="s">
-        <v>64</v>
+      <c r="E28" s="6">
+        <v>13603839494</v>
       </c>
       <c r="F28">
         <v>3</v>
       </c>
       <c r="G28" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2080,22 +2002,22 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>66</v>
+      <c r="E29" s="6">
+        <v>18039355500</v>
       </c>
       <c r="F29">
         <v>5</v>
       </c>
       <c r="G29" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2122,8 +2044,5 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <ignoredErrors>
-    <ignoredError sqref="E3:E29 E12" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/107女生宿舍名单.xlsx
+++ b/107女生宿舍名单.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\infomation-of-107\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\infomation-of-107\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,11 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="41">
-  <si>
-    <t>107班主任纪亚东
-17611228667</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="40">
   <si>
     <t>序号</t>
   </si>
@@ -842,30 +838,27 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1402,7 +1395,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="12.625"/>
@@ -1410,635 +1403,621 @@
     <col min="7" max="7" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" ht="14.25" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" ht="14.25" spans="1:7">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
       <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="4">
+        <v>15729279897</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="4">
+        <v>15703933753</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="4">
+        <v>13939363372</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="4">
+        <v>13598736538</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="4">
+        <v>13673021779</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="G2" t="s">
+      <c r="B7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="4">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="4">
+        <v>18639341832</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="4">
+        <v>13461656277</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="6">
-        <v>15729279897</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="6">
-        <v>15703933753</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="6">
-        <v>13939363372</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="6">
-        <v>13598736538</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="4">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="6">
-        <v>13673021779</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="6">
-        <v>18639341832</v>
-      </c>
-      <c r="F8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="4">
+      <c r="B9" t="s">
         <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="4">
+        <v>13839351366</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="4">
+        <v>13721799805</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="E9" s="6">
-        <v>13461656277</v>
-      </c>
-      <c r="F9">
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="4">
+        <v>13653933521</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="4">
+        <v>15539326958</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="4">
+        <v>13949735762</v>
+      </c>
+      <c r="F13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="4">
+        <v>18568818855</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+      <c r="G14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="6">
+        <v>13903937336</v>
+      </c>
+      <c r="F15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="4">
+        <v>15839336710</v>
+      </c>
+      <c r="F16">
         <v>7</v>
       </c>
-      <c r="G9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
+      <c r="G16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="4">
+        <v>19639399998</v>
+      </c>
+      <c r="F17">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="7" t="s">
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="4">
+        <v>15936754215</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="D10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="6">
-        <v>13839351366</v>
-      </c>
-      <c r="F10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="4">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="4">
+        <v>13525618067</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="4">
+        <v>13939392757</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="6">
-        <v>13721799805</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="4">
+        <v>13461709630</v>
+      </c>
+      <c r="F21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="D12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="6">
-        <v>13653933521</v>
-      </c>
-      <c r="F12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="4">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="4">
+        <v>13783934087</v>
+      </c>
+      <c r="F22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="D13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="6">
-        <v>15539326958</v>
-      </c>
-      <c r="F13">
-        <v>3</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="4">
+        <v>13938309563</v>
+      </c>
+      <c r="F23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="D14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="6">
-        <v>13949735762</v>
-      </c>
-      <c r="F14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="4">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="6">
-        <v>18568818855</v>
-      </c>
-      <c r="F15">
-        <v>5</v>
-      </c>
-      <c r="G15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="2">
-        <v>13903937336</v>
-      </c>
-      <c r="F16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="4">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="6">
-        <v>15839336710</v>
-      </c>
-      <c r="F17">
-        <v>7</v>
-      </c>
-      <c r="G17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="5" t="s">
+      <c r="B24" t="s">
         <v>27</v>
-      </c>
-      <c r="D18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="6">
-        <v>19639399998</v>
-      </c>
-      <c r="F18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="4">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="6">
-        <v>15936754215</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="6">
-        <v>13525618067</v>
-      </c>
-      <c r="F20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="4">
-        <v>19</v>
-      </c>
-      <c r="B21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="6">
-        <v>13939392757</v>
-      </c>
-      <c r="F21">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20</v>
-      </c>
-      <c r="B22" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="6">
-        <v>13461709630</v>
-      </c>
-      <c r="F22">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="4">
-        <v>21</v>
-      </c>
-      <c r="B23" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="6">
-        <v>13783934087</v>
-      </c>
-      <c r="F23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22</v>
-      </c>
-      <c r="B24" t="s">
-        <v>28</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="6">
-        <v>13938309563</v>
+        <v>9</v>
+      </c>
+      <c r="E24" s="4">
+        <v>18239371983</v>
       </c>
       <c r="F24">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="G24" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="4">
-        <v>23</v>
+      <c r="A25">
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D25" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="6">
-        <v>18239371983</v>
+        <v>9</v>
+      </c>
+      <c r="E25" s="4">
+        <v>13461702187</v>
       </c>
       <c r="F25">
-        <v>7</v>
-      </c>
-      <c r="G25" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26">
-        <v>24</v>
+      <c r="A26" s="2">
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C26" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="4">
+        <v>15939323292</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
         <v>36</v>
       </c>
-      <c r="D26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="6">
-        <v>13461702187</v>
-      </c>
-      <c r="F26">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="4">
-        <v>25</v>
-      </c>
-      <c r="B27" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" s="6">
-        <v>15939323292</v>
+        <v>9</v>
+      </c>
+      <c r="E27" s="4">
+        <v>13603839494</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28">
-        <v>26</v>
+      <c r="A28" s="2">
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>39</v>
       </c>
       <c r="D28" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" s="6">
-        <v>13603839494</v>
+        <v>9</v>
+      </c>
+      <c r="E28" s="4">
+        <v>18039355500</v>
       </c>
       <c r="F28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="4">
-        <v>27</v>
-      </c>
-      <c r="B29" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D29" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="6">
-        <v>18039355500</v>
-      </c>
-      <c r="F29">
-        <v>5</v>
-      </c>
-      <c r="G29" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="4"/>
+      <c r="A29" s="2"/>
     </row>
   </sheetData>
   <sortState ref="A3:G30">
     <sortCondition ref="A3"/>
   </sortState>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C25">
+  <conditionalFormatting sqref="C24">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C28">
+  <conditionalFormatting sqref="C27">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C24 C26:C27 C29">
+  <conditionalFormatting sqref="C2:C23 C25:C26 C28">
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
